--- a/Evaluation/score_eval/supine_score_GT.xlsx
+++ b/Evaluation/score_eval/supine_score_GT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dvirbuss\PycharmProjects\infant-analyzer-app\Evaluation\score_eval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18BD046-1032-4395-B6D7-5D5009716564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021A4415-79B7-4B82-AEA5-626C93816694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5385" yWindow="2520" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>video_name</t>
   </si>
@@ -71,7 +71,37 @@
     <t>Rolling Supine to Prone With Rotation</t>
   </si>
   <si>
-    <t>supine_video_1</t>
+    <t>supine_video_01</t>
+  </si>
+  <si>
+    <t>supine_video_02</t>
+  </si>
+  <si>
+    <t>supine_video_03</t>
+  </si>
+  <si>
+    <t>supine_video_04</t>
+  </si>
+  <si>
+    <t>supine_video_05</t>
+  </si>
+  <si>
+    <t>supine_video_06</t>
+  </si>
+  <si>
+    <t>supine_video_13</t>
+  </si>
+  <si>
+    <t>supine_video_14</t>
+  </si>
+  <si>
+    <t>supine_video_15</t>
+  </si>
+  <si>
+    <t>supine_video_20</t>
+  </si>
+  <si>
+    <t>supine_video_21</t>
   </si>
 </sst>
 </file>
@@ -95,7 +125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +135,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -136,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -145,6 +181,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -427,10 +466,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultColWidth="15.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="8" width="15.42578125" style="2"/>
+    <col min="1" max="1" width="17.42578125" style="2" customWidth="1"/>
+    <col min="2" max="8" width="15.42578125" style="2"/>
     <col min="9" max="9" width="34.7109375" style="2" customWidth="1"/>
     <col min="10" max="10" width="32.42578125" style="2" customWidth="1"/>
     <col min="11" max="16384" width="15.42578125" style="2"/>
@@ -472,8 +512,8 @@
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -484,10 +524,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+        <v>11</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -498,10 +538,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -512,10 +552,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
+        <v>13</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -526,10 +566,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
+        <v>14</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -540,10 +580,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -554,10 +594,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -568,10 +608,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+        <v>17</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -582,10 +622,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+        <v>18</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -596,59 +636,59 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+        <v>19</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+        <v>20</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
